--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/52.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/52.xlsx
@@ -426,13 +426,13 @@
         <v>-6.058721374209229</v>
       </c>
       <c r="E2">
-        <v>-14.23832589672256</v>
+        <v>-13.55673621688008</v>
       </c>
       <c r="F2">
-        <v>-0.6350207996617891</v>
+        <v>0.1935802027453059</v>
       </c>
       <c r="G2">
-        <v>-11.4904167982327</v>
+        <v>-12.86918937873293</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.676386489188407</v>
       </c>
       <c r="E3">
-        <v>-14.18534275083282</v>
+        <v>-13.56517276395637</v>
       </c>
       <c r="F3">
-        <v>0.0424752196984397</v>
+        <v>0.5655544431354099</v>
       </c>
       <c r="G3">
-        <v>-11.84436216785</v>
+        <v>-12.76892509154098</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.245760234878987</v>
       </c>
       <c r="E4">
-        <v>-15.38536572049543</v>
+        <v>-15.09567018127674</v>
       </c>
       <c r="F4">
-        <v>0.06797485345881688</v>
+        <v>0.8571488809622667</v>
       </c>
       <c r="G4">
-        <v>-12.12524129578159</v>
+        <v>-13.17123894816605</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.815213049306827</v>
       </c>
       <c r="E5">
-        <v>-15.93234651045991</v>
+        <v>-14.31646924419892</v>
       </c>
       <c r="F5">
-        <v>0.08448255906180542</v>
+        <v>0.1682520410373082</v>
       </c>
       <c r="G5">
-        <v>-12.01990424005874</v>
+        <v>-12.56829808051029</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.392009276654455</v>
       </c>
       <c r="E6">
-        <v>-17.1502524239788</v>
+        <v>-15.60106599442878</v>
       </c>
       <c r="F6">
-        <v>0.1110118535038624</v>
+        <v>1.032264093179277</v>
       </c>
       <c r="G6">
-        <v>-12.28017401537545</v>
+        <v>-11.81811895781756</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.997114346361482</v>
       </c>
       <c r="E7">
-        <v>-16.5993001623096</v>
+        <v>-15.44767752284097</v>
       </c>
       <c r="F7">
-        <v>0.1512050682550972</v>
+        <v>1.475014872831973</v>
       </c>
       <c r="G7">
-        <v>-12.18389641237822</v>
+        <v>-11.05264278021471</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.637030111465671</v>
       </c>
       <c r="E8">
-        <v>-18.0168166816126</v>
+        <v>-15.80772290576882</v>
       </c>
       <c r="F8">
-        <v>0.3529763151267924</v>
+        <v>1.096677942420966</v>
       </c>
       <c r="G8">
-        <v>-11.90845426857064</v>
+        <v>-12.07693187076189</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.327212408518863</v>
       </c>
       <c r="E9">
-        <v>-18.98077935820336</v>
+        <v>-18.06890771812283</v>
       </c>
       <c r="F9">
-        <v>0.2807973498512603</v>
+        <v>1.388004817576719</v>
       </c>
       <c r="G9">
-        <v>-10.77616048917278</v>
+        <v>-10.92445857877344</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.071170302539133</v>
       </c>
       <c r="E10">
-        <v>-18.69169969144972</v>
+        <v>-18.37049955855966</v>
       </c>
       <c r="F10">
-        <v>0.2851760999424585</v>
+        <v>1.689051755836921</v>
       </c>
       <c r="G10">
-        <v>-10.52102582559659</v>
+        <v>-11.85471442187005</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.870447491604333</v>
       </c>
       <c r="E11">
-        <v>-18.82029929631954</v>
+        <v>-18.14346451418511</v>
       </c>
       <c r="F11">
-        <v>-0.03207121961429341</v>
+        <v>2.067912214446497</v>
       </c>
       <c r="G11">
-        <v>-10.26145495047204</v>
+        <v>-11.0721660484934</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.722135859689265</v>
       </c>
       <c r="E12">
-        <v>-19.99127663369695</v>
+        <v>-20.43319229820947</v>
       </c>
       <c r="F12">
-        <v>0.1782438086498759</v>
+        <v>1.484739906140839</v>
       </c>
       <c r="G12">
-        <v>-9.879763571348073</v>
+        <v>-10.7112710516132</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.61899070316054</v>
       </c>
       <c r="E13">
-        <v>-21.48507982613316</v>
+        <v>-21.03397588785908</v>
       </c>
       <c r="F13">
-        <v>0.9374143688239276</v>
+        <v>1.536426718605917</v>
       </c>
       <c r="G13">
-        <v>-9.500874355435874</v>
+        <v>-8.835160438126373</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.560295971361594</v>
       </c>
       <c r="E14">
-        <v>-22.09221686481553</v>
+        <v>-20.93841602934922</v>
       </c>
       <c r="F14">
-        <v>0.6339933295873023</v>
+        <v>1.053672420337227</v>
       </c>
       <c r="G14">
-        <v>-8.376882066583407</v>
+        <v>-8.270002836727615</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.540549265543391</v>
       </c>
       <c r="E15">
-        <v>-22.63282156337721</v>
+        <v>-24.33018871940622</v>
       </c>
       <c r="F15">
-        <v>0.8147397834085432</v>
+        <v>1.890368229004479</v>
       </c>
       <c r="G15">
-        <v>-8.258715434563126</v>
+        <v>-7.530067687743475</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.55280762473224</v>
       </c>
       <c r="E16">
-        <v>-24.12347746637809</v>
+        <v>-22.45444044374107</v>
       </c>
       <c r="F16">
-        <v>0.7741216161796722</v>
+        <v>1.688029550461866</v>
       </c>
       <c r="G16">
-        <v>-7.540757907584146</v>
+        <v>-7.597083356873574</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.589096979510022</v>
       </c>
       <c r="E17">
-        <v>-23.41023828169601</v>
+        <v>-22.9838009413417</v>
       </c>
       <c r="F17">
-        <v>0.5049759349686821</v>
+        <v>1.599926050234916</v>
       </c>
       <c r="G17">
-        <v>-6.961382773168315</v>
+        <v>-7.338250756599897</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.638467835897349</v>
       </c>
       <c r="E18">
-        <v>-25.28130864371123</v>
+        <v>-24.55407194587144</v>
       </c>
       <c r="F18">
-        <v>0.9054609246283395</v>
+        <v>2.322264082210891</v>
       </c>
       <c r="G18">
-        <v>-6.689969969435726</v>
+        <v>-8.091944067582789</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.69595784466979</v>
       </c>
       <c r="E19">
-        <v>-25.58902298100644</v>
+        <v>-23.30352026323125</v>
       </c>
       <c r="F19">
-        <v>0.7968950928174362</v>
+        <v>1.693705523905848</v>
       </c>
       <c r="G19">
-        <v>-6.076657160430558</v>
+        <v>-7.890322846419589</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.755372265067916</v>
       </c>
       <c r="E20">
-        <v>-26.62029689524722</v>
+        <v>-24.90364296841954</v>
       </c>
       <c r="F20">
-        <v>1.186081979470311</v>
+        <v>2.645428430125839</v>
       </c>
       <c r="G20">
-        <v>-5.435903495523752</v>
+        <v>-5.973771177212609</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.811764966169393</v>
       </c>
       <c r="E21">
-        <v>-25.9659595719829</v>
+        <v>-26.99728329943776</v>
       </c>
       <c r="F21">
-        <v>1.508065075468868</v>
+        <v>3.404280897217216</v>
       </c>
       <c r="G21">
-        <v>-5.807301682615741</v>
+        <v>-4.917923297706691</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.862556823943978</v>
       </c>
       <c r="E22">
-        <v>-27.33190130081254</v>
+        <v>-27.68585135772607</v>
       </c>
       <c r="F22">
-        <v>1.321185389397299</v>
+        <v>2.224205262537096</v>
       </c>
       <c r="G22">
-        <v>-4.663526908981383</v>
+        <v>-5.417151314311526</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.905048470901039</v>
       </c>
       <c r="E23">
-        <v>-27.56247761186109</v>
+        <v>-27.29621239715809</v>
       </c>
       <c r="F23">
-        <v>1.168233975409593</v>
+        <v>2.82439058056145</v>
       </c>
       <c r="G23">
-        <v>-4.697671300528964</v>
+        <v>-6.549182595984631</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.942082948864894</v>
       </c>
       <c r="E24">
-        <v>-28.89899331658889</v>
+        <v>-26.57868927606475</v>
       </c>
       <c r="F24">
-        <v>1.677684898335706</v>
+        <v>2.844423817830753</v>
       </c>
       <c r="G24">
-        <v>-4.861794721710829</v>
+        <v>-5.027565316115536</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.976303956823963</v>
       </c>
       <c r="E25">
-        <v>-28.72877250711457</v>
+        <v>-26.42378376568437</v>
       </c>
       <c r="F25">
-        <v>1.699687993288866</v>
+        <v>3.149713653928095</v>
       </c>
       <c r="G25">
-        <v>-4.225956326700073</v>
+        <v>-5.598619272656616</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.00989577090386</v>
       </c>
       <c r="E26">
-        <v>-28.99208515676457</v>
+        <v>-28.51544968203524</v>
       </c>
       <c r="F26">
-        <v>0.9875007754667969</v>
+        <v>3.589248711323124</v>
       </c>
       <c r="G26">
-        <v>-4.189150864467782</v>
+        <v>-4.11913944005391</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.044756947699168</v>
       </c>
       <c r="E27">
-        <v>-28.2675202585893</v>
+        <v>-26.94860673232932</v>
       </c>
       <c r="F27">
-        <v>1.434315525597628</v>
+        <v>3.826822825711216</v>
       </c>
       <c r="G27">
-        <v>-4.160128459774493</v>
+        <v>-6.650342656662312</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.079864512878189</v>
       </c>
       <c r="E28">
-        <v>-29.04543510904894</v>
+        <v>-29.11698046989612</v>
       </c>
       <c r="F28">
-        <v>1.730736860280597</v>
+        <v>3.16039130975018</v>
       </c>
       <c r="G28">
-        <v>-3.751754186929123</v>
+        <v>-4.696992087666159</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.11717618705026</v>
       </c>
       <c r="E29">
-        <v>-28.00780321730139</v>
+        <v>-28.11855610610698</v>
       </c>
       <c r="F29">
-        <v>1.40546017548851</v>
+        <v>3.463194386904317</v>
       </c>
       <c r="G29">
-        <v>-4.287170796113074</v>
+        <v>-3.976993640877205</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.157593705659608</v>
       </c>
       <c r="E30">
-        <v>-27.57635285622059</v>
+        <v>-28.45565571123797</v>
       </c>
       <c r="F30">
-        <v>1.765288064651365</v>
+        <v>3.119095537985819</v>
       </c>
       <c r="G30">
-        <v>-4.578471083717456</v>
+        <v>-4.926707127821325</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.200515697509272</v>
       </c>
       <c r="E31">
-        <v>-27.66439997635173</v>
+        <v>-27.56447919737248</v>
       </c>
       <c r="F31">
-        <v>1.651544936572965</v>
+        <v>2.51108214800501</v>
       </c>
       <c r="G31">
-        <v>-4.11157622435939</v>
+        <v>-4.622439452614016</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.244436910375434</v>
       </c>
       <c r="E32">
-        <v>-27.71169535888784</v>
+        <v>-25.90192242104044</v>
       </c>
       <c r="F32">
-        <v>1.322159549462992</v>
+        <v>3.250877194627581</v>
       </c>
       <c r="G32">
-        <v>-4.369253834644143</v>
+        <v>-5.484826508975074</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.284720751697393</v>
       </c>
       <c r="E33">
-        <v>-27.53163870386886</v>
+        <v>-25.81291526441968</v>
       </c>
       <c r="F33">
-        <v>1.26458635823362</v>
+        <v>3.529576437095058</v>
       </c>
       <c r="G33">
-        <v>-4.834189804731222</v>
+        <v>-4.536858631900579</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.319278497105246</v>
       </c>
       <c r="E34">
-        <v>-26.56558387228655</v>
+        <v>-25.70416848959948</v>
       </c>
       <c r="F34">
-        <v>1.391425974950281</v>
+        <v>2.341268487165917</v>
       </c>
       <c r="G34">
-        <v>-5.435598341918724</v>
+        <v>-5.283832001129728</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.345296113552952</v>
       </c>
       <c r="E35">
-        <v>-26.33421054981265</v>
+        <v>-25.93063294624907</v>
       </c>
       <c r="F35">
-        <v>1.603141772492584</v>
+        <v>3.244462317460302</v>
       </c>
       <c r="G35">
-        <v>-5.571267009737085</v>
+        <v>-7.331389722319098</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.359056097782192</v>
       </c>
       <c r="E36">
-        <v>-25.49486242096496</v>
+        <v>-25.86078123468075</v>
       </c>
       <c r="F36">
-        <v>1.116149546591171</v>
+        <v>3.214014845203003</v>
       </c>
       <c r="G36">
-        <v>-5.159342455164396</v>
+        <v>-7.001197115570617</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.357682138177102</v>
       </c>
       <c r="E37">
-        <v>-25.1989855147258</v>
+        <v>-25.43342008562889</v>
       </c>
       <c r="F37">
-        <v>1.733967493151515</v>
+        <v>3.224313108754607</v>
       </c>
       <c r="G37">
-        <v>-5.729520325549103</v>
+        <v>-6.401589969019248</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.33803279880011</v>
       </c>
       <c r="E38">
-        <v>-24.76010845627242</v>
+        <v>-23.43135455599377</v>
       </c>
       <c r="F38">
-        <v>1.650181443827957</v>
+        <v>2.920848994413036</v>
       </c>
       <c r="G38">
-        <v>-6.690626213747615</v>
+        <v>-8.252399083061194</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.302345052872727</v>
       </c>
       <c r="E39">
-        <v>-24.6576019186348</v>
+        <v>-24.05610283009198</v>
       </c>
       <c r="F39">
-        <v>1.848550585776354</v>
+        <v>4.016533871565553</v>
       </c>
       <c r="G39">
-        <v>-6.605983822400179</v>
+        <v>-8.793666110285635</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.255912276478314</v>
       </c>
       <c r="E40">
-        <v>-22.93221256544632</v>
+        <v>-24.24372656517777</v>
       </c>
       <c r="F40">
-        <v>1.715264613931108</v>
+        <v>3.668407500334644</v>
       </c>
       <c r="G40">
-        <v>-6.604586022015855</v>
+        <v>-8.273205308969633</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.205504521366087</v>
       </c>
       <c r="E41">
-        <v>-24.20066530583884</v>
+        <v>-22.13176855679853</v>
       </c>
       <c r="F41">
-        <v>2.371374672053262</v>
+        <v>3.792664267489375</v>
       </c>
       <c r="G41">
-        <v>-7.244936096670848</v>
+        <v>-7.336331241987621</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.15972298091364</v>
       </c>
       <c r="E42">
-        <v>-22.227690693229</v>
+        <v>-22.05189986072524</v>
       </c>
       <c r="F42">
-        <v>1.770592929498893</v>
+        <v>3.065564779682109</v>
       </c>
       <c r="G42">
-        <v>-7.776467739528417</v>
+        <v>-8.356289120076333</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.125885278980237</v>
       </c>
       <c r="E43">
-        <v>-22.28776090094075</v>
+        <v>-22.18910809468365</v>
       </c>
       <c r="F43">
-        <v>1.938607376339105</v>
+        <v>3.267505841871379</v>
       </c>
       <c r="G43">
-        <v>-7.591794027719749</v>
+        <v>-8.398147663510169</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.113954455261954</v>
       </c>
       <c r="E44">
-        <v>-21.67830981204045</v>
+        <v>-23.68930549241869</v>
       </c>
       <c r="F44">
-        <v>2.291856371588926</v>
+        <v>3.010007834711152</v>
       </c>
       <c r="G44">
-        <v>-7.908057848948387</v>
+        <v>-9.540593542412951</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.1339145042539</v>
       </c>
       <c r="E45">
-        <v>-21.15167092731843</v>
+        <v>-21.46764067272962</v>
       </c>
       <c r="F45">
-        <v>2.672691658086777</v>
+        <v>2.830616589960891</v>
       </c>
       <c r="G45">
-        <v>-8.368009643486669</v>
+        <v>-9.602634879658932</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.192160072808046</v>
       </c>
       <c r="E46">
-        <v>-20.21638707661824</v>
+        <v>-17.10209663138124</v>
       </c>
       <c r="F46">
-        <v>2.653130590237069</v>
+        <v>3.867046690056354</v>
       </c>
       <c r="G46">
-        <v>-7.836681436365787</v>
+        <v>-8.59946373106834</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.292129971118642</v>
       </c>
       <c r="E47">
-        <v>-20.05517340194518</v>
+        <v>-18.88873359552345</v>
       </c>
       <c r="F47">
-        <v>2.231789794477129</v>
+        <v>2.857006718679278</v>
       </c>
       <c r="G47">
-        <v>-8.196247538514417</v>
+        <v>-8.6892904524797</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.431637434487813</v>
       </c>
       <c r="E48">
-        <v>-17.84243420452523</v>
+        <v>-18.80496135485556</v>
       </c>
       <c r="F48">
-        <v>2.615776190575228</v>
+        <v>3.606801816588445</v>
       </c>
       <c r="G48">
-        <v>-9.031416862039881</v>
+        <v>-7.530290810809517</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.607481181510646</v>
       </c>
       <c r="E49">
-        <v>-18.68245254752605</v>
+        <v>-17.51479005312226</v>
       </c>
       <c r="F49">
-        <v>2.266867840516077</v>
+        <v>3.019823988434327</v>
       </c>
       <c r="G49">
-        <v>-8.75552519087865</v>
+        <v>-8.730614156799346</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.815775259077304</v>
       </c>
       <c r="E50">
-        <v>-18.0812296958977</v>
+        <v>-19.19407954091265</v>
       </c>
       <c r="F50">
-        <v>2.518057001536582</v>
+        <v>4.075511973910072</v>
       </c>
       <c r="G50">
-        <v>-8.634907486353463</v>
+        <v>-9.261489555345024</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.048299934746318</v>
       </c>
       <c r="E51">
-        <v>-16.03777391383248</v>
+        <v>-16.96236150892655</v>
       </c>
       <c r="F51">
-        <v>2.470033229726683</v>
+        <v>3.653316302990443</v>
       </c>
       <c r="G51">
-        <v>-8.961933714297079</v>
+        <v>-9.818171761455737</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.295368646415444</v>
       </c>
       <c r="E52">
-        <v>-15.61211094253349</v>
+        <v>-16.86290263429609</v>
       </c>
       <c r="F52">
-        <v>2.949197383671641</v>
+        <v>3.901814926686655</v>
       </c>
       <c r="G52">
-        <v>-8.910100257322531</v>
+        <v>-8.453409997014337</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.544479825646263</v>
       </c>
       <c r="E53">
-        <v>-15.3307387385409</v>
+        <v>-15.47952175206291</v>
       </c>
       <c r="F53">
-        <v>2.356570089830429</v>
+        <v>3.291231941022362</v>
       </c>
       <c r="G53">
-        <v>-9.570784061981403</v>
+        <v>-10.02197171373441</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.784931298746035</v>
       </c>
       <c r="E54">
-        <v>-14.35747004786437</v>
+        <v>-14.34514354161549</v>
       </c>
       <c r="F54">
-        <v>2.407052456091837</v>
+        <v>3.472665939787927</v>
       </c>
       <c r="G54">
-        <v>-9.122562634518136</v>
+        <v>-9.293025375752848</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.010293507088581</v>
       </c>
       <c r="E55">
-        <v>-14.93303909423927</v>
+        <v>-13.07686741170928</v>
       </c>
       <c r="F55">
-        <v>2.546892470828033</v>
+        <v>3.056953072162606</v>
       </c>
       <c r="G55">
-        <v>-9.489048832935636</v>
+        <v>-9.078617234172492</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.213712692410872</v>
       </c>
       <c r="E56">
-        <v>-14.37285327406843</v>
+        <v>-15.30477246858092</v>
       </c>
       <c r="F56">
-        <v>2.467915922645128</v>
+        <v>2.240331919134797</v>
       </c>
       <c r="G56">
-        <v>-9.067188739480947</v>
+        <v>-9.917829022659193</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.390532202557271</v>
       </c>
       <c r="E57">
-        <v>-13.43135182855571</v>
+        <v>-13.66228588905086</v>
       </c>
       <c r="F57">
-        <v>2.284513722930511</v>
+        <v>3.22414246506963</v>
       </c>
       <c r="G57">
-        <v>-10.25533219104212</v>
+        <v>-10.43264284167139</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.536312692583696</v>
       </c>
       <c r="E58">
-        <v>-12.26542373969685</v>
+        <v>-11.78574060196036</v>
       </c>
       <c r="F58">
-        <v>2.099154919410483</v>
+        <v>3.096015565409019</v>
       </c>
       <c r="G58">
-        <v>-9.389772193433076</v>
+        <v>-10.52438907769502</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.649729791839976</v>
       </c>
       <c r="E59">
-        <v>-12.7265446624759</v>
+        <v>-13.28207973984087</v>
       </c>
       <c r="F59">
-        <v>2.180407821216281</v>
+        <v>3.464388892699154</v>
       </c>
       <c r="G59">
-        <v>-10.31611353920927</v>
+        <v>-9.356398888951963</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.735493959022834</v>
       </c>
       <c r="E60">
-        <v>-12.77316983085887</v>
+        <v>-11.61868972429141</v>
       </c>
       <c r="F60">
-        <v>1.881241276960434</v>
+        <v>2.824014501760579</v>
       </c>
       <c r="G60">
-        <v>-10.27112799162928</v>
+        <v>-10.4435725906859</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.797102248809904</v>
       </c>
       <c r="E61">
-        <v>-11.25899756233616</v>
+        <v>-10.52787090532377</v>
       </c>
       <c r="F61">
-        <v>2.218398407043472</v>
+        <v>3.238317488066335</v>
       </c>
       <c r="G61">
-        <v>-9.724194294771682</v>
+        <v>-10.10159055487433</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.83884435912527</v>
       </c>
       <c r="E62">
-        <v>-11.13009907818183</v>
+        <v>-11.30775564197675</v>
       </c>
       <c r="F62">
-        <v>1.844049237309542</v>
+        <v>2.776494377331583</v>
       </c>
       <c r="G62">
-        <v>-10.29968774408269</v>
+        <v>-9.709504265850047</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.863191740064894</v>
       </c>
       <c r="E63">
-        <v>-11.69748970049888</v>
+        <v>-10.32937430414556</v>
       </c>
       <c r="F63">
-        <v>1.893279112057916</v>
+        <v>2.996323205216904</v>
       </c>
       <c r="G63">
-        <v>-9.831703519166886</v>
+        <v>-10.42798350705698</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.873545320686041</v>
       </c>
       <c r="E64">
-        <v>-9.730936464031918</v>
+        <v>-8.220178664910987</v>
       </c>
       <c r="F64">
-        <v>1.838129723849136</v>
+        <v>3.360417186504177</v>
       </c>
       <c r="G64">
-        <v>-9.963562688754733</v>
+        <v>-10.6515692253391</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.878374107129325</v>
       </c>
       <c r="E65">
-        <v>-10.66332661984121</v>
+        <v>-11.14866582161328</v>
       </c>
       <c r="F65">
-        <v>1.821012339837687</v>
+        <v>2.933136996466164</v>
       </c>
       <c r="G65">
-        <v>-10.39184085157969</v>
+        <v>-10.49012328094974</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.882852558376096</v>
       </c>
       <c r="E66">
-        <v>-9.797160867920091</v>
+        <v>-9.653042182625981</v>
       </c>
       <c r="F66">
-        <v>1.375978579622875</v>
+        <v>2.802869595436719</v>
       </c>
       <c r="G66">
-        <v>-9.575364647278388</v>
+        <v>-9.862464971286681</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.891422773470323</v>
       </c>
       <c r="E67">
-        <v>-9.234004368800212</v>
+        <v>-10.03298115186952</v>
       </c>
       <c r="F67">
-        <v>1.454148297955454</v>
+        <v>2.402093848818679</v>
       </c>
       <c r="G67">
-        <v>-9.823510308932955</v>
+        <v>-10.8932640054078</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.905606979705756</v>
       </c>
       <c r="E68">
-        <v>-9.986197486896282</v>
+        <v>-9.691149291400528</v>
       </c>
       <c r="F68">
-        <v>1.393011470159239</v>
+        <v>2.528539162651607</v>
       </c>
       <c r="G68">
-        <v>-9.575633707446261</v>
+        <v>-10.19374366237134</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.926042766789821</v>
       </c>
       <c r="E69">
-        <v>-9.602604039128549</v>
+        <v>-8.996110043755266</v>
       </c>
       <c r="F69">
-        <v>1.272472415908272</v>
+        <v>2.388362830749875</v>
       </c>
       <c r="G69">
-        <v>-10.12134350866219</v>
+        <v>-10.78161387940457</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.95927732730657</v>
       </c>
       <c r="E70">
-        <v>-10.32038075476632</v>
+        <v>-10.48094232918228</v>
       </c>
       <c r="F70">
-        <v>1.310322179276987</v>
+        <v>2.859932512345966</v>
       </c>
       <c r="G70">
-        <v>-8.842264282802571</v>
+        <v>-8.302601772920699</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.007373705140265</v>
       </c>
       <c r="E71">
-        <v>-9.344648574229621</v>
+        <v>-9.650116788417026</v>
       </c>
       <c r="F71">
-        <v>0.7533047433473207</v>
+        <v>2.203626959516751</v>
       </c>
       <c r="G71">
-        <v>-8.079924953010542</v>
+        <v>-8.713797896307192</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.0716309384903</v>
       </c>
       <c r="E72">
-        <v>-9.253381709079035</v>
+        <v>-9.470703176707135</v>
       </c>
       <c r="F72">
-        <v>0.9013339982275923</v>
+        <v>2.147349334905358</v>
       </c>
       <c r="G72">
-        <v>-8.828273154073099</v>
+        <v>-9.779889749521695</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.150439886199697</v>
       </c>
       <c r="E73">
-        <v>-9.586360402863034</v>
+        <v>-9.10522815344409</v>
       </c>
       <c r="F73">
-        <v>0.7837439319305913</v>
+        <v>2.026777145958279</v>
       </c>
       <c r="G73">
-        <v>-7.795413512812651</v>
+        <v>-9.697426089289731</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.240254817926576</v>
       </c>
       <c r="E74">
-        <v>-9.539608437207846</v>
+        <v>-9.635476231950229</v>
       </c>
       <c r="F74">
-        <v>1.074167886617292</v>
+        <v>2.54458960944825</v>
       </c>
       <c r="G74">
-        <v>-7.939377108733288</v>
+        <v>-9.844011381236365</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.344698446451644</v>
       </c>
       <c r="E75">
-        <v>-9.504050859299619</v>
+        <v>-9.651344004873105</v>
       </c>
       <c r="F75">
-        <v>0.5266965566374879</v>
+        <v>1.399149672613983</v>
       </c>
       <c r="G75">
-        <v>-7.218978352914081</v>
+        <v>-9.211217959832773</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.462584258358205</v>
       </c>
       <c r="E76">
-        <v>-9.089392079839268</v>
+        <v>-8.862877809975595</v>
       </c>
       <c r="F76">
-        <v>0.4515387821814887</v>
+        <v>1.788078108637185</v>
       </c>
       <c r="G76">
-        <v>-7.556786674902034</v>
+        <v>-8.521836591414997</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.59245706134333</v>
       </c>
       <c r="E77">
-        <v>-10.22427747937554</v>
+        <v>-11.50101732720209</v>
       </c>
       <c r="F77">
-        <v>-0.05379515475271045</v>
+        <v>1.879781693596701</v>
       </c>
       <c r="G77">
-        <v>-7.298078761047615</v>
+        <v>-7.498758271623254</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.731045332130523</v>
       </c>
       <c r="E78">
-        <v>-10.6730628389577</v>
+        <v>-11.39439440669149</v>
       </c>
       <c r="F78">
-        <v>0.4697653501452863</v>
+        <v>2.020885796989569</v>
       </c>
       <c r="G78">
-        <v>-7.502817142692287</v>
+        <v>-8.129041558533871</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.872990899379087</v>
       </c>
       <c r="E79">
-        <v>-10.92440673180543</v>
+        <v>-11.59203965475627</v>
       </c>
       <c r="F79">
-        <v>0.602077990292243</v>
+        <v>1.862223618126963</v>
       </c>
       <c r="G79">
-        <v>-5.638472989717632</v>
+        <v>-8.256126550752724</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.023505764725207</v>
       </c>
       <c r="E80">
-        <v>-11.15885035965653</v>
+        <v>-12.0029081014722</v>
       </c>
       <c r="F80">
-        <v>0.1406052789688747</v>
+        <v>1.551517915950119</v>
       </c>
       <c r="G80">
-        <v>-5.588801857750758</v>
+        <v>-7.779647243219519</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.183420703209832</v>
       </c>
       <c r="E81">
-        <v>-11.55058147521605</v>
+        <v>-11.94981627220627</v>
       </c>
       <c r="F81">
-        <v>-0.1583665989473144</v>
+        <v>2.16574571818673</v>
       </c>
       <c r="G81">
-        <v>-5.647096039975852</v>
+        <v>-7.011595306692497</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.353867718086907</v>
       </c>
       <c r="E82">
-        <v>-13.34824980204095</v>
+        <v>-12.15916762558087</v>
       </c>
       <c r="F82">
-        <v>-0.2389129033585244</v>
+        <v>1.678407234710947</v>
       </c>
       <c r="G82">
-        <v>-5.72340084734074</v>
+        <v>-7.576198381647709</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.534280394634061</v>
       </c>
       <c r="E83">
-        <v>-13.33075630694932</v>
+        <v>-12.31062696724142</v>
       </c>
       <c r="F83">
-        <v>-0.2755590488909717</v>
+        <v>1.503104811460904</v>
       </c>
       <c r="G83">
-        <v>-5.185339573579876</v>
+        <v>-7.738592599067746</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.719369355860803</v>
       </c>
       <c r="E84">
-        <v>-14.93723246117038</v>
+        <v>-14.57856826281487</v>
       </c>
       <c r="F84">
-        <v>-0.5760907426266323</v>
+        <v>1.154135162213946</v>
       </c>
       <c r="G84">
-        <v>-4.222524168948894</v>
+        <v>-6.216637353378029</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.915925614289587</v>
       </c>
       <c r="E85">
-        <v>-14.89637656867317</v>
+        <v>-14.31738399594847</v>
       </c>
       <c r="F85">
-        <v>-0.4368198162961598</v>
+        <v>1.807804849967452</v>
       </c>
       <c r="G85">
-        <v>-4.438382610458524</v>
+        <v>-5.277299089004874</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.124706754825272</v>
       </c>
       <c r="E86">
-        <v>-16.69087496369271</v>
+        <v>-17.18610888117154</v>
       </c>
       <c r="F86">
-        <v>-0.6104381686163111</v>
+        <v>0.1359399137563079</v>
       </c>
       <c r="G86">
-        <v>-4.668730926374662</v>
+        <v>-6.217237816923407</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.346230798078601</v>
       </c>
       <c r="E87">
-        <v>-17.67129411482735</v>
+        <v>-18.37791719898423</v>
       </c>
       <c r="F87">
-        <v>-0.8016469027349097</v>
+        <v>0.9706252747369654</v>
       </c>
       <c r="G87">
-        <v>-4.102543021406238</v>
+        <v>-5.494384707377736</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.579546644393075</v>
       </c>
       <c r="E88">
-        <v>-17.87709061610592</v>
+        <v>-19.5895511760025</v>
       </c>
       <c r="F88">
-        <v>-0.7437481631162383</v>
+        <v>1.228703139079151</v>
       </c>
       <c r="G88">
-        <v>-3.871079090159889</v>
+        <v>-7.732752024691934</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.816914750038496</v>
       </c>
       <c r="E89">
-        <v>-20.70233309390734</v>
+        <v>-18.55372614538402</v>
       </c>
       <c r="F89">
-        <v>-1.281477064071718</v>
+        <v>0.6109299243585584</v>
       </c>
       <c r="G89">
-        <v>-4.404759933138894</v>
+        <v>-5.383420356680435</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.066057547133427</v>
       </c>
       <c r="E90">
-        <v>-21.26906708749328</v>
+        <v>-23.24389384597225</v>
       </c>
       <c r="F90">
-        <v>-1.545652540865911</v>
+        <v>0.2845283166334692</v>
       </c>
       <c r="G90">
-        <v>-4.332317123549474</v>
+        <v>-5.45536113937126</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.327785711986825</v>
       </c>
       <c r="E91">
-        <v>-22.06216591130063</v>
+        <v>-22.51486840089942</v>
       </c>
       <c r="F91">
-        <v>-1.565461290569055</v>
+        <v>0.4040534491834099</v>
       </c>
       <c r="G91">
-        <v>-3.630260396247563</v>
+        <v>-5.200308506334062</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.603024137163658</v>
       </c>
       <c r="E92">
-        <v>-25.05460870641325</v>
+        <v>-24.03339253294351</v>
       </c>
       <c r="F92">
-        <v>-1.757111544513346</v>
+        <v>-0.02477910136744936</v>
       </c>
       <c r="G92">
-        <v>-4.176108008768989</v>
+        <v>-5.093091310657647</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.891809089993464</v>
       </c>
       <c r="E93">
-        <v>-26.1084163073162</v>
+        <v>-25.54343936164523</v>
       </c>
       <c r="F93">
-        <v>-1.540830614214215</v>
+        <v>-0.01981055368545793</v>
       </c>
       <c r="G93">
-        <v>-4.060999475242109</v>
+        <v>-7.076110684994299</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.18552760138769</v>
       </c>
       <c r="E94">
-        <v>-27.81107724946017</v>
+        <v>-29.59496316564273</v>
       </c>
       <c r="F94">
-        <v>-2.143742917728585</v>
+        <v>-0.5537082554029897</v>
       </c>
       <c r="G94">
-        <v>-4.143581259450213</v>
+        <v>-6.277418701545182</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.49351284952116</v>
       </c>
       <c r="E95">
-        <v>-30.42086625516165</v>
+        <v>-30.16698868110663</v>
       </c>
       <c r="F95">
-        <v>-2.675331959494514</v>
+        <v>-0.4340505840686011</v>
       </c>
       <c r="G95">
-        <v>-4.918881414402049</v>
+        <v>-5.690742849159586</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.81687531179331</v>
       </c>
       <c r="E96">
-        <v>-31.96806694885931</v>
+        <v>-30.68584311900947</v>
       </c>
       <c r="F96">
-        <v>-2.686220020636911</v>
+        <v>-0.9530028811048242</v>
       </c>
       <c r="G96">
-        <v>-4.542492489318145</v>
+        <v>-6.631620006444121</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.15221175545113</v>
       </c>
       <c r="E97">
-        <v>-34.18217600966658</v>
+        <v>-34.74482984817161</v>
       </c>
       <c r="F97">
-        <v>-2.48342905349237</v>
+        <v>-0.70461028843617</v>
       </c>
       <c r="G97">
-        <v>-5.166679266571314</v>
+        <v>-6.598187639974938</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.49692753046548</v>
       </c>
       <c r="E98">
-        <v>-36.11165462943274</v>
+        <v>-36.88759959369904</v>
       </c>
       <c r="F98">
-        <v>-2.858138563046518</v>
+        <v>-1.0175310450481</v>
       </c>
       <c r="G98">
-        <v>-5.14584022844728</v>
+        <v>-7.083378590748469</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.83004414785411</v>
       </c>
       <c r="E99">
-        <v>-38.27816037147139</v>
+        <v>-38.20345413576685</v>
       </c>
       <c r="F99">
-        <v>-2.872575350142507</v>
+        <v>-0.4845693984957318</v>
       </c>
       <c r="G99">
-        <v>-5.400653332310638</v>
+        <v>-7.789946997694615</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.15735427375053</v>
       </c>
       <c r="E100">
-        <v>-40.30163652621476</v>
+        <v>-40.05489129872182</v>
       </c>
       <c r="F100">
-        <v>-3.030205383221225</v>
+        <v>-0.7625868945907046</v>
       </c>
       <c r="G100">
-        <v>-6.576091893993637</v>
+        <v>-7.980969873220809</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.45826771563228</v>
       </c>
       <c r="E101">
-        <v>-42.92000019744976</v>
+        <v>-42.116030771787</v>
       </c>
       <c r="F101">
-        <v>-3.121219766501612</v>
+        <v>-0.7831188090364932</v>
       </c>
       <c r="G101">
-        <v>-6.130912158915976</v>
+        <v>-8.076899666732734</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.73574415580852</v>
       </c>
       <c r="E102">
-        <v>-43.63378279901277</v>
+        <v>-46.28649041712195</v>
       </c>
       <c r="F102">
-        <v>-3.057106614627139</v>
+        <v>-1.562823768758542</v>
       </c>
       <c r="G102">
-        <v>-7.087909957722062</v>
+        <v>-7.683500889084669</v>
       </c>
     </row>
   </sheetData>
